--- a/椙山改修/チェック/様式_図面チェック.xlsx
+++ b/椙山改修/チェック/様式_図面チェック.xlsx
@@ -505,14 +505,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,30 +555,38 @@
       <c r="B4" s="4" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>チェック日</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n"/>
+          <t>平山さん宛て要（構造確認）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>チェック日</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>件数（要修正／要確認／参考）</t>
+        </is>
+      </c>
+      <c r="E5" s="7">
+        <f>COUNTIF($E$9:$E$500,"要修正")&amp;"／"&amp;COUNTIF($E$9:$E$500,"要確認")&amp;"／"&amp;COUNTIF($E$9:$E$500,"参考")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
           <t>チェック者</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>件数（要修正／要確認／参考）</t>
-        </is>
-      </c>
-      <c r="E5" s="7">
-        <f>COUNTIF($B$9:$B$500,"要修正")&amp;"／"&amp;COUNTIF($B$9:$B$500,"要確認")&amp;"／"&amp;COUNTIF($B$9:$B$500,"参考")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>区分：要修正＝図面の訂正が必要／要確認＝設計者・業者への確認が必要／参考＝気づき・提案</t>
         </is>
@@ -593,608 +600,553 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>頁</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>箇所</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>指摘内容</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>図面番号・頁</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>部位・箇所</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>指摘内容</t>
-        </is>
-      </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>根拠（設計図・特記・基準）</t>
+          <t>根拠（図面番号・仕様書の項目）</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>回答・対応</t>
+          <t>対応</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>確認日</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>状態</t>
+          <t>対応日</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n"/>
       <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
+      <c r="C9" s="10" t="n"/>
       <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="n"/>
+      <c r="E9" s="9" t="n"/>
       <c r="F9" s="10" t="n"/>
       <c r="G9" s="10" t="n"/>
       <c r="H9" s="11" t="n"/>
-      <c r="I9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n"/>
       <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="10" t="n"/>
       <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
+      <c r="E10" s="9" t="n"/>
       <c r="F10" s="10" t="n"/>
       <c r="G10" s="10" t="n"/>
       <c r="H10" s="11" t="n"/>
-      <c r="I10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n"/>
       <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
+      <c r="C11" s="10" t="n"/>
       <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
+      <c r="E11" s="9" t="n"/>
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="11" t="n"/>
-      <c r="I11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n"/>
       <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
+      <c r="C12" s="10" t="n"/>
       <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
+      <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n"/>
       <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
+      <c r="C13" s="10" t="n"/>
       <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
+      <c r="E13" s="9" t="n"/>
       <c r="F13" s="10" t="n"/>
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="11" t="n"/>
-      <c r="I13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n"/>
       <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
+      <c r="C14" s="10" t="n"/>
       <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
+      <c r="E14" s="9" t="n"/>
       <c r="F14" s="10" t="n"/>
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="11" t="n"/>
-      <c r="I14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n"/>
       <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
+      <c r="C15" s="10" t="n"/>
       <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
+      <c r="E15" s="9" t="n"/>
       <c r="F15" s="10" t="n"/>
       <c r="G15" s="10" t="n"/>
       <c r="H15" s="11" t="n"/>
-      <c r="I15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n"/>
       <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
+      <c r="C16" s="10" t="n"/>
       <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
+      <c r="E16" s="9" t="n"/>
       <c r="F16" s="10" t="n"/>
       <c r="G16" s="10" t="n"/>
       <c r="H16" s="11" t="n"/>
-      <c r="I16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n"/>
       <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
+      <c r="C17" s="10" t="n"/>
       <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="E17" s="9" t="n"/>
       <c r="F17" s="10" t="n"/>
       <c r="G17" s="10" t="n"/>
       <c r="H17" s="11" t="n"/>
-      <c r="I17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n"/>
       <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
+      <c r="C18" s="10" t="n"/>
       <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
+      <c r="E18" s="9" t="n"/>
       <c r="F18" s="10" t="n"/>
       <c r="G18" s="10" t="n"/>
       <c r="H18" s="11" t="n"/>
-      <c r="I18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n"/>
       <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
+      <c r="C19" s="10" t="n"/>
       <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
+      <c r="E19" s="9" t="n"/>
       <c r="F19" s="10" t="n"/>
       <c r="G19" s="10" t="n"/>
       <c r="H19" s="11" t="n"/>
-      <c r="I19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n"/>
       <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
+      <c r="C20" s="10" t="n"/>
       <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
+      <c r="E20" s="9" t="n"/>
       <c r="F20" s="10" t="n"/>
       <c r="G20" s="10" t="n"/>
       <c r="H20" s="11" t="n"/>
-      <c r="I20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n"/>
       <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
+      <c r="C21" s="10" t="n"/>
       <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
+      <c r="E21" s="9" t="n"/>
       <c r="F21" s="10" t="n"/>
       <c r="G21" s="10" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n"/>
       <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
+      <c r="C22" s="10" t="n"/>
       <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
+      <c r="E22" s="9" t="n"/>
       <c r="F22" s="10" t="n"/>
       <c r="G22" s="10" t="n"/>
       <c r="H22" s="11" t="n"/>
-      <c r="I22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n"/>
       <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
+      <c r="C23" s="10" t="n"/>
       <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="n"/>
+      <c r="E23" s="9" t="n"/>
       <c r="F23" s="10" t="n"/>
       <c r="G23" s="10" t="n"/>
       <c r="H23" s="11" t="n"/>
-      <c r="I23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n"/>
       <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
+      <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
+      <c r="E24" s="9" t="n"/>
       <c r="F24" s="10" t="n"/>
       <c r="G24" s="10" t="n"/>
       <c r="H24" s="11" t="n"/>
-      <c r="I24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n"/>
       <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
+      <c r="C25" s="10" t="n"/>
       <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
+      <c r="E25" s="9" t="n"/>
       <c r="F25" s="10" t="n"/>
       <c r="G25" s="10" t="n"/>
       <c r="H25" s="11" t="n"/>
-      <c r="I25" s="9" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n"/>
       <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
+      <c r="C26" s="10" t="n"/>
       <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
+      <c r="E26" s="9" t="n"/>
       <c r="F26" s="10" t="n"/>
       <c r="G26" s="10" t="n"/>
       <c r="H26" s="11" t="n"/>
-      <c r="I26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n"/>
       <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
+      <c r="C27" s="10" t="n"/>
       <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
+      <c r="E27" s="9" t="n"/>
       <c r="F27" s="10" t="n"/>
       <c r="G27" s="10" t="n"/>
       <c r="H27" s="11" t="n"/>
-      <c r="I27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="n"/>
       <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
+      <c r="C28" s="10" t="n"/>
       <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
+      <c r="E28" s="9" t="n"/>
       <c r="F28" s="10" t="n"/>
       <c r="G28" s="10" t="n"/>
       <c r="H28" s="11" t="n"/>
-      <c r="I28" s="9" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n"/>
       <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
+      <c r="C29" s="10" t="n"/>
       <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
+      <c r="E29" s="9" t="n"/>
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="10" t="n"/>
       <c r="H29" s="11" t="n"/>
-      <c r="I29" s="9" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n"/>
       <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
+      <c r="C30" s="10" t="n"/>
       <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
+      <c r="E30" s="9" t="n"/>
       <c r="F30" s="10" t="n"/>
       <c r="G30" s="10" t="n"/>
       <c r="H30" s="11" t="n"/>
-      <c r="I30" s="9" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="9" t="n"/>
       <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
+      <c r="C31" s="10" t="n"/>
       <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
+      <c r="E31" s="9" t="n"/>
       <c r="F31" s="10" t="n"/>
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="11" t="n"/>
-      <c r="I31" s="9" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="n"/>
       <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
+      <c r="C32" s="10" t="n"/>
       <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
+      <c r="E32" s="9" t="n"/>
       <c r="F32" s="10" t="n"/>
       <c r="G32" s="10" t="n"/>
       <c r="H32" s="11" t="n"/>
-      <c r="I32" s="9" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="n"/>
       <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
+      <c r="C33" s="10" t="n"/>
       <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
+      <c r="E33" s="9" t="n"/>
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="11" t="n"/>
-      <c r="I33" s="9" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="9" t="n"/>
       <c r="B34" s="9" t="n"/>
-      <c r="C34" s="9" t="n"/>
+      <c r="C34" s="10" t="n"/>
       <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
+      <c r="E34" s="9" t="n"/>
       <c r="F34" s="10" t="n"/>
       <c r="G34" s="10" t="n"/>
       <c r="H34" s="11" t="n"/>
-      <c r="I34" s="9" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="9" t="n"/>
       <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
+      <c r="C35" s="10" t="n"/>
       <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
+      <c r="E35" s="9" t="n"/>
       <c r="F35" s="10" t="n"/>
       <c r="G35" s="10" t="n"/>
       <c r="H35" s="11" t="n"/>
-      <c r="I35" s="9" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="n"/>
       <c r="B36" s="9" t="n"/>
-      <c r="C36" s="9" t="n"/>
+      <c r="C36" s="10" t="n"/>
       <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
+      <c r="E36" s="9" t="n"/>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="10" t="n"/>
       <c r="H36" s="11" t="n"/>
-      <c r="I36" s="9" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="n"/>
       <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
+      <c r="C37" s="10" t="n"/>
       <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
+      <c r="E37" s="9" t="n"/>
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="10" t="n"/>
       <c r="H37" s="11" t="n"/>
-      <c r="I37" s="9" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="9" t="n"/>
       <c r="B38" s="9" t="n"/>
-      <c r="C38" s="9" t="n"/>
+      <c r="C38" s="10" t="n"/>
       <c r="D38" s="10" t="n"/>
-      <c r="E38" s="10" t="n"/>
+      <c r="E38" s="9" t="n"/>
       <c r="F38" s="10" t="n"/>
       <c r="G38" s="10" t="n"/>
       <c r="H38" s="11" t="n"/>
-      <c r="I38" s="9" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="9" t="n"/>
       <c r="B39" s="9" t="n"/>
-      <c r="C39" s="9" t="n"/>
+      <c r="C39" s="10" t="n"/>
       <c r="D39" s="10" t="n"/>
-      <c r="E39" s="10" t="n"/>
+      <c r="E39" s="9" t="n"/>
       <c r="F39" s="10" t="n"/>
       <c r="G39" s="10" t="n"/>
       <c r="H39" s="11" t="n"/>
-      <c r="I39" s="9" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="9" t="n"/>
       <c r="B40" s="9" t="n"/>
-      <c r="C40" s="9" t="n"/>
+      <c r="C40" s="10" t="n"/>
       <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
+      <c r="E40" s="9" t="n"/>
       <c r="F40" s="10" t="n"/>
       <c r="G40" s="10" t="n"/>
       <c r="H40" s="11" t="n"/>
-      <c r="I40" s="9" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="9" t="n"/>
       <c r="B41" s="9" t="n"/>
-      <c r="C41" s="9" t="n"/>
+      <c r="C41" s="10" t="n"/>
       <c r="D41" s="10" t="n"/>
-      <c r="E41" s="10" t="n"/>
+      <c r="E41" s="9" t="n"/>
       <c r="F41" s="10" t="n"/>
       <c r="G41" s="10" t="n"/>
       <c r="H41" s="11" t="n"/>
-      <c r="I41" s="9" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="9" t="n"/>
       <c r="B42" s="9" t="n"/>
-      <c r="C42" s="9" t="n"/>
+      <c r="C42" s="10" t="n"/>
       <c r="D42" s="10" t="n"/>
-      <c r="E42" s="10" t="n"/>
+      <c r="E42" s="9" t="n"/>
       <c r="F42" s="10" t="n"/>
       <c r="G42" s="10" t="n"/>
       <c r="H42" s="11" t="n"/>
-      <c r="I42" s="9" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="9" t="n"/>
       <c r="B43" s="9" t="n"/>
-      <c r="C43" s="9" t="n"/>
+      <c r="C43" s="10" t="n"/>
       <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
+      <c r="E43" s="9" t="n"/>
       <c r="F43" s="10" t="n"/>
       <c r="G43" s="10" t="n"/>
       <c r="H43" s="11" t="n"/>
-      <c r="I43" s="9" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="9" t="n"/>
       <c r="B44" s="9" t="n"/>
-      <c r="C44" s="9" t="n"/>
+      <c r="C44" s="10" t="n"/>
       <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
+      <c r="E44" s="9" t="n"/>
       <c r="F44" s="10" t="n"/>
       <c r="G44" s="10" t="n"/>
       <c r="H44" s="11" t="n"/>
-      <c r="I44" s="9" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="9" t="n"/>
       <c r="B45" s="9" t="n"/>
-      <c r="C45" s="9" t="n"/>
+      <c r="C45" s="10" t="n"/>
       <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
+      <c r="E45" s="9" t="n"/>
       <c r="F45" s="10" t="n"/>
       <c r="G45" s="10" t="n"/>
       <c r="H45" s="11" t="n"/>
-      <c r="I45" s="9" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="9" t="n"/>
       <c r="B46" s="9" t="n"/>
-      <c r="C46" s="9" t="n"/>
+      <c r="C46" s="10" t="n"/>
       <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
+      <c r="E46" s="9" t="n"/>
       <c r="F46" s="10" t="n"/>
       <c r="G46" s="10" t="n"/>
       <c r="H46" s="11" t="n"/>
-      <c r="I46" s="9" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="9" t="n"/>
       <c r="B47" s="9" t="n"/>
-      <c r="C47" s="9" t="n"/>
+      <c r="C47" s="10" t="n"/>
       <c r="D47" s="10" t="n"/>
-      <c r="E47" s="10" t="n"/>
+      <c r="E47" s="9" t="n"/>
       <c r="F47" s="10" t="n"/>
       <c r="G47" s="10" t="n"/>
       <c r="H47" s="11" t="n"/>
-      <c r="I47" s="9" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="9" t="n"/>
       <c r="B48" s="9" t="n"/>
-      <c r="C48" s="9" t="n"/>
+      <c r="C48" s="10" t="n"/>
       <c r="D48" s="10" t="n"/>
-      <c r="E48" s="10" t="n"/>
+      <c r="E48" s="9" t="n"/>
       <c r="F48" s="10" t="n"/>
       <c r="G48" s="10" t="n"/>
       <c r="H48" s="11" t="n"/>
-      <c r="I48" s="9" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="9" t="n"/>
       <c r="B49" s="9" t="n"/>
-      <c r="C49" s="9" t="n"/>
+      <c r="C49" s="10" t="n"/>
       <c r="D49" s="10" t="n"/>
-      <c r="E49" s="10" t="n"/>
+      <c r="E49" s="9" t="n"/>
       <c r="F49" s="10" t="n"/>
       <c r="G49" s="10" t="n"/>
       <c r="H49" s="11" t="n"/>
-      <c r="I49" s="9" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="9" t="n"/>
       <c r="B50" s="9" t="n"/>
-      <c r="C50" s="9" t="n"/>
+      <c r="C50" s="10" t="n"/>
       <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
+      <c r="E50" s="9" t="n"/>
       <c r="F50" s="10" t="n"/>
       <c r="G50" s="10" t="n"/>
       <c r="H50" s="11" t="n"/>
-      <c r="I50" s="9" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="9" t="n"/>
       <c r="B51" s="9" t="n"/>
-      <c r="C51" s="9" t="n"/>
+      <c r="C51" s="10" t="n"/>
       <c r="D51" s="10" t="n"/>
-      <c r="E51" s="10" t="n"/>
+      <c r="E51" s="9" t="n"/>
       <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
       <c r="H51" s="11" t="n"/>
-      <c r="I51" s="9" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="9" t="n"/>
       <c r="B52" s="9" t="n"/>
-      <c r="C52" s="9" t="n"/>
+      <c r="C52" s="10" t="n"/>
       <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
+      <c r="E52" s="9" t="n"/>
       <c r="F52" s="10" t="n"/>
       <c r="G52" s="10" t="n"/>
       <c r="H52" s="11" t="n"/>
-      <c r="I52" s="9" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="9" t="n"/>
       <c r="B53" s="9" t="n"/>
-      <c r="C53" s="9" t="n"/>
+      <c r="C53" s="10" t="n"/>
       <c r="D53" s="10" t="n"/>
-      <c r="E53" s="10" t="n"/>
+      <c r="E53" s="9" t="n"/>
       <c r="F53" s="10" t="n"/>
       <c r="G53" s="10" t="n"/>
       <c r="H53" s="11" t="n"/>
-      <c r="I53" s="9" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="9" t="n"/>
       <c r="B54" s="9" t="n"/>
-      <c r="C54" s="9" t="n"/>
+      <c r="C54" s="10" t="n"/>
       <c r="D54" s="10" t="n"/>
-      <c r="E54" s="10" t="n"/>
+      <c r="E54" s="9" t="n"/>
       <c r="F54" s="10" t="n"/>
       <c r="G54" s="10" t="n"/>
       <c r="H54" s="11" t="n"/>
-      <c r="I54" s="9" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="9" t="n"/>
       <c r="B55" s="9" t="n"/>
-      <c r="C55" s="9" t="n"/>
+      <c r="C55" s="10" t="n"/>
       <c r="D55" s="10" t="n"/>
-      <c r="E55" s="10" t="n"/>
+      <c r="E55" s="9" t="n"/>
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
       <c r="H55" s="11" t="n"/>
-      <c r="I55" s="9" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="9" t="n"/>
       <c r="B56" s="9" t="n"/>
-      <c r="C56" s="9" t="n"/>
+      <c r="C56" s="10" t="n"/>
       <c r="D56" s="10" t="n"/>
-      <c r="E56" s="10" t="n"/>
+      <c r="E56" s="9" t="n"/>
       <c r="F56" s="10" t="n"/>
       <c r="G56" s="10" t="n"/>
       <c r="H56" s="11" t="n"/>
-      <c r="I56" s="9" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="9" t="n"/>
       <c r="B57" s="9" t="n"/>
-      <c r="C57" s="9" t="n"/>
+      <c r="C57" s="10" t="n"/>
       <c r="D57" s="10" t="n"/>
-      <c r="E57" s="10" t="n"/>
+      <c r="E57" s="9" t="n"/>
       <c r="F57" s="10" t="n"/>
       <c r="G57" s="10" t="n"/>
       <c r="H57" s="11" t="n"/>
-      <c r="I57" s="9" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="9" t="n"/>
       <c r="B58" s="9" t="n"/>
-      <c r="C58" s="9" t="n"/>
+      <c r="C58" s="10" t="n"/>
       <c r="D58" s="10" t="n"/>
-      <c r="E58" s="10" t="n"/>
+      <c r="E58" s="9" t="n"/>
       <c r="F58" s="10" t="n"/>
       <c r="G58" s="10" t="n"/>
       <c r="H58" s="11" t="n"/>
-      <c r="I58" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="E3:I3"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="B9:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E9:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"要修正,要確認,参考"</formula1>
     </dataValidation>
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"打,打２,受,受２"</formula1>
     </dataValidation>
-    <dataValidation sqref="I9:I500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"未対応,対応済,確認済"</formula1>
+    <dataValidation sqref="E4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"要,不要"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1208,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1347,7 +1299,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>前回の監理者・現場の指摘（返却コメント）がすべて反映されている</t>
+          <t>前回指摘（NS確認の返却コメント）がすべて反映されている</t>
         </is>
       </c>
       <c r="E8" s="9" t="n"/>
@@ -1809,7 +1761,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>部材の割付・ジョイント位置・取付けピッチ</t>
+          <t>構造確認が必要なもの（天井下地・鉄骨等）は「平山さん宛て要」を記入（2026/10/14 監理者依頼）</t>
         </is>
       </c>
       <c r="E29" s="9" t="n"/>
@@ -1831,7 +1783,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>アンカー・ボルト・溶接の仕様（径・本数・溶接長）、既存躯体への固定方法</t>
+          <t>部材の割付・ジョイント位置・取付けピッチ</t>
         </is>
       </c>
       <c r="E30" s="9" t="n"/>
@@ -1853,7 +1805,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>構造確認が必要なもの（天井下地・吊り物・鉄骨下地）は計算書の有無と結果</t>
+          <t>アンカー・ボルト・溶接の仕様（径・本数・溶接長）、既存躯体への固定方法</t>
         </is>
       </c>
       <c r="E31" s="9" t="n"/>
@@ -1875,7 +1827,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>建具：有効寸法・開き勝手・金物（丁番・錠・クローザー・自動ドア機構）・気密/水密等級</t>
+          <t>構造確認が必要なもの（天井下地・吊り物・鉄骨下地）は計算書の有無と結果</t>
         </is>
       </c>
       <c r="E32" s="9" t="n"/>
@@ -1897,7 +1849,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>建具：ガラス種別・厚さ、防火設備の認定番号</t>
+          <t>建具：有効寸法・開き勝手・金物（丁番・錠・クローザー・自動ドア機構）・気密/水密等級</t>
         </is>
       </c>
       <c r="E33" s="9" t="n"/>
@@ -1919,7 +1871,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>可動部・重量物の振れ止め・脱落防止</t>
+          <t>建具：ガラス種別・厚さ、防火設備の認定番号</t>
         </is>
       </c>
       <c r="E34" s="9" t="n"/>
@@ -1941,7 +1893,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>製作・搬入・揚重の可否（部材寸法・重量・分割位置）</t>
+          <t>可動部・重量物の振れ止め・脱落防止</t>
         </is>
       </c>
       <c r="E35" s="9" t="n"/>
@@ -1963,7 +1915,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>色・仕上げサンプル承認の要否、製作期間と施工予定日の整合</t>
+          <t>製作・搬入・揚重の可否（部材寸法・重量・分割位置）</t>
         </is>
       </c>
       <c r="E36" s="9" t="n"/>
@@ -1975,17 +1927,17 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>法規・安全</t>
+          <t>製作図（鉄骨下地・建具・金物・ルーバー等）</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>共</t>
+          <t>製</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>内装制限・不燃/準不燃材料の認定番号</t>
+          <t>色・仕上げサンプル承認の要否、製作期間と施工予定日の整合</t>
         </is>
       </c>
       <c r="E37" s="9" t="n"/>
@@ -2007,7 +1959,7 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>建築基準法・消防法・条例上の必要事項（避難・排煙・非常照明への影響）</t>
+          <t>内装制限・不燃/準不燃材料の認定番号</t>
         </is>
       </c>
       <c r="E38" s="9" t="n"/>
@@ -2029,15 +1981,37 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>供用中施設（大学）の動線・安全への配慮（夜間・休日作業、養生）</t>
+          <t>建築基準法・消防法・条例上の必要事項（避難・排煙・非常照明への影響）</t>
         </is>
       </c>
       <c r="E39" s="9" t="n"/>
       <c r="F39" s="10" t="n"/>
     </row>
+    <row r="40">
+      <c r="A40" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>法規・安全</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>共</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>供用中施設（大学）の動線・安全への配慮（夜間・休日作業、養生）</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="10" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"〇,×,－"</formula1>
     </dataValidation>
   </dataValidations>

--- a/椙山改修/チェック/様式_図面チェック.xlsx
+++ b/椙山改修/チェック/様式_図面チェック.xlsx
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2009,9 +2009,405 @@
       <c r="E40" s="9" t="n"/>
       <c r="F40" s="10" t="n"/>
     </row>
+    <row r="41">
+      <c r="A41" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>共</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>【提出】施工図・機器製作図は工事期間中に3部提出（発注者・監理者保管・受注者返却）。基準施工図（建具図等）・総合図も3部（要領26 0.2表 期間中No.4〜6、0.3(4)）</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>共</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>【提出】施工図工程表・施工図検討フロー（監理業務マップ）は監理者の指示により監理者と協同で作成（要領26 0.2表 期間中No.1）</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>共</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>【書式】図面枠の書式は監理者と協議して決める（要領26 2.4(1)）</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>共</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>【承認】建築工事の施工図は監理者に提出し、別に定めがなければ監理者の承認を受ける。項目が挙がっていない工種も同じ（要領26 5.1 1(1)）</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>共</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>【一覧表】施工図等の一覧表と工程表を監理者に提出（①②リストで代用できるか監理者と確認）（要領26 5.1 1(2)）</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="10" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>共</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>【改修工事】改修工事は 5.1 の章番号によらず、該当する事項を準用する（要領26 5.1 1(3)）</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>施</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>【基準施工図】総合図に先立ち基準施工図（床仕上げ・スラブレベル図、間仕切種別図、建具納まり図など）を作り監理者の承認を受ける（要領26 4.1）</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="10" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>施</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>【総合図】平面図・監理者が指示する室の天井伏図・展開図を元図に、設備の部品・器具を記入（原則 1/50）。「総合図の手引き2023」参照（要領26 4.2）</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="10" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>共</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>【シーリング】施工箇所・材料・目地の形状寸法・異種シーリングの交わり・他工事との関連。主要部分は建具・タイル等の施工図にも併記。ワーキングジョイントは目地寸法を計算（要領26 5.1 9章(2)(3)）</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>施</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>【タイル（仕上-5 など）】使用材料・割付け・張りしろ・出隅入隅・伸縮調整目地・ひび割れ誘発目地・はく離防止・関連工事取合い。割付けは設計図書等又は監理者の指示による（要領26 5.1 11章）</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="10" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>製</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>【金属・天井下地（三友ほか）】使用材料・表面処理・溶接の種類と寸法・納まり。天井下地は吊りボルト位置・耐震ブレース位置・他工事とのクリアランス、特定天井は計算。LGS壁は層間変形・異音防止・遮音・開口補強。手すりは強度指定があれば強度計算書（構造確認は平山さん宛て）（要領26 5.1 14章）</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>施</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>【左官】下地・下地補強・材料・割付け・塗り厚・伸縮目地・開口部周り・取合い（要領26 5.1 15章）</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>製</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>【建具（三和シャッター・三和タジマ）】平面（前後の室名・床レベル・天井高）・材料・防火区画・ガラス種別厚・金物・シーリング・他工事との関連。スライド式自動ドアは JIS A4722（挟まれ・衝突防止）。ガラリ・アンダーカットの開口面積。性能検討書（耐風圧・水密等の計算、熱割れ計算、強化ガラス使用範囲など）を添付。鍵はキーシステムプランと鍵の種類のプロット図（要領26 5.1 16章）</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="10" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>製</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>【ハンガードア・移動間仕切】移動時の振動・騒音対策、他部材との取合い・遮音、ハンガーレール取付け下地の補強、耐震・遮音性能を満たす計算（三和-1・三友-24 に関係）（要領26 5.1 20章 20.2.4）</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>製</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>【木工事（ミディック）】継手・仕口、材料とホルムアルデヒド放散量、金物・接着剤、変形への考慮、設備との取合い（要領26 5.1 12章）</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>施</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>【内装】監理者の指示で各種割付け図。システム天井は天井下地図（吊りボルト・耐震ブレース・落下防止）（要領26 5.1 19章）</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="n"/>
+      <c r="F56" s="10" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>共</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>【天井内検査】天井ボード等を張る前に、建築・設備合同で自主検査を行い、検査記録を監理者に提出して監理者の検査を受ける（天井下地・耐震ブレース・クリアランス、区画貫通処理、設備の支持・耐震固定など a〜n）（要領26 第2部 1.2(1)1)イ）</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="10" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>日建要領26（日建設計 提出書類作成要領・受注者検査要領26。参考/日建設計_提出書類作成要領・受注者検査要領26.pdf）</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>共</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>【完成時】施工図は発注者に提出し、一覧表を竣工引継ぎ書に入れる。主要な製作図・製作要領書もファイルにして提出（要領26 3.5(2)(3)）</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="10" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"〇,×,－"</formula1>
     </dataValidation>
   </dataValidations>
